--- a/artfynd/A 35767-2025 artfynd.xlsx
+++ b/artfynd/A 35767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130794753</v>
       </c>
       <c r="B2" t="n">
-        <v>98887</v>
+        <v>98888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35767-2025 artfynd.xlsx
+++ b/artfynd/A 35767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130794753</v>
       </c>
       <c r="B2" t="n">
-        <v>98888</v>
+        <v>98891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35767-2025 artfynd.xlsx
+++ b/artfynd/A 35767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130794753</v>
       </c>
       <c r="B2" t="n">
-        <v>98891</v>
+        <v>98905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35767-2025 artfynd.xlsx
+++ b/artfynd/A 35767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130794753</v>
       </c>
       <c r="B2" t="n">
-        <v>98905</v>
+        <v>98906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35767-2025 artfynd.xlsx
+++ b/artfynd/A 35767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130794753</v>
       </c>
       <c r="B2" t="n">
-        <v>98906</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35767-2025 artfynd.xlsx
+++ b/artfynd/A 35767-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130794753</v>
+        <v>130794752</v>
       </c>
       <c r="B2" t="n">
-        <v>98930</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388025</v>
+        <v>388045</v>
       </c>
       <c r="R2" t="n">
-        <v>6627806</v>
+        <v>6627783</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,6 +774,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130794753</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Finnfallet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>388025</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6627806</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Måttlig förekomst. Inventering åt tekniska verken.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sofia Berg, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
